--- a/declaration_forms/028_declaration_of_presence_form--declaration_forms.xlsx
+++ b/declaration_forms/028_declaration_of_presence_form--declaration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -962,8 +962,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -991,12 +991,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'walk'}</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Walk'}</t>
+          <t>Walk</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'drive'}</t>
+          <t>drive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Drive'}</t>
+          <t>Drive</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'by_bike'}</t>
+          <t>by_bike</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'By Bike'}</t>
+          <t>By Bike</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'School'}</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
